--- a/Proyecto_1/DATA/equip_rep_est.xlsx
+++ b/Proyecto_1/DATA/equip_rep_est.xlsx
@@ -681,10 +681,10 @@
         <v>872</v>
       </c>
       <c r="B6" t="n">
-        <v>60.23405963302752</v>
+        <v>60.23061926605504</v>
       </c>
       <c r="C6" t="n">
-        <v>10.95225408801221</v>
+        <v>10.95582704974701</v>
       </c>
       <c r="D6" t="n">
         <v>22.8</v>
@@ -696,7 +696,7 @@
         <v>53.075</v>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>61.05</v>
       </c>
       <c r="H6" t="n">
         <v>68.40000000000001</v>
@@ -725,10 +725,10 @@
         <v>872</v>
       </c>
       <c r="B7" t="n">
-        <v>10.19495412844037</v>
+        <v>10.19724770642202</v>
       </c>
       <c r="C7" t="n">
-        <v>3.521438001818126</v>
+        <v>3.522288127927228</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1209,10 +1209,10 @@
         <v>872</v>
       </c>
       <c r="B18" t="n">
-        <v>514.0298165137615</v>
+        <v>514.7878440366973</v>
       </c>
       <c r="C18" t="n">
-        <v>133.8020850429812</v>
+        <v>134.1638230001124</v>
       </c>
       <c r="D18" t="n">
         <v>148</v>
@@ -1224,10 +1224,10 @@
         <v>421</v>
       </c>
       <c r="G18" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="H18" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I18" t="n">
         <v>686</v>
@@ -1242,10 +1242,10 @@
         <v>972</v>
       </c>
       <c r="M18" t="n">
-        <v>142</v>
+        <v>140.5</v>
       </c>
       <c r="N18" t="n">
-        <v>886</v>
+        <v>888.5</v>
       </c>
     </row>
     <row r="19">
@@ -1253,10 +1253,10 @@
         <v>872</v>
       </c>
       <c r="B19" t="n">
-        <v>581.190366972477</v>
+        <v>581.8457568807339</v>
       </c>
       <c r="C19" t="n">
-        <v>131.8778285088847</v>
+        <v>132.2022964705175</v>
       </c>
       <c r="D19" t="n">
         <v>208</v>
@@ -1268,10 +1268,10 @@
         <v>489</v>
       </c>
       <c r="G19" t="n">
-        <v>576</v>
+        <v>580.5</v>
       </c>
       <c r="H19" t="n">
-        <v>671.25</v>
+        <v>672.25</v>
       </c>
       <c r="I19" t="n">
         <v>752.9</v>
@@ -1286,10 +1286,10 @@
         <v>1030</v>
       </c>
       <c r="M19" t="n">
-        <v>215.625</v>
+        <v>214.125</v>
       </c>
       <c r="N19" t="n">
-        <v>944.625</v>
+        <v>947.125</v>
       </c>
     </row>
     <row r="20">
@@ -1476,7 +1476,7 @@
         <v>42.5355504587156</v>
       </c>
       <c r="C24" t="n">
-        <v>11.31131830756636</v>
+        <v>11.32204690835209</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
         <v>872</v>
       </c>
       <c r="B25" t="n">
-        <v>23.13990825688073</v>
+        <v>23.16685779816514</v>
       </c>
       <c r="C25" t="n">
-        <v>7.715739887544126</v>
+        <v>7.72128376314799</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -1561,10 +1561,10 @@
         <v>872</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5480504587155963</v>
+        <v>0.5493119266055045</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1289215435276542</v>
+        <v>0.1289344619247673</v>
       </c>
       <c r="D26" t="n">
         <v>0.2</v>
@@ -1649,10 +1649,10 @@
         <v>872</v>
       </c>
       <c r="B28" t="n">
-        <v>9.529816513761467</v>
+        <v>9.540137614678899</v>
       </c>
       <c r="C28" t="n">
-        <v>3.377378784196825</v>
+        <v>3.378291469536264</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1737,10 +1737,10 @@
         <v>872</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6182339449541283</v>
+        <v>0.618577981651376</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1334006347925852</v>
+        <v>0.1334821835970159</v>
       </c>
       <c r="D30" t="n">
         <v>0.2</v>
@@ -1781,10 +1781,10 @@
         <v>872</v>
       </c>
       <c r="B31" t="n">
-        <v>7.407110091743119</v>
+        <v>7.409403669724771</v>
       </c>
       <c r="C31" t="n">
-        <v>3.193793478350626</v>
+        <v>3.196374756545364</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1825,10 +1825,10 @@
         <v>872</v>
       </c>
       <c r="B32" t="n">
-        <v>16.61582568807339</v>
+        <v>16.61295871559633</v>
       </c>
       <c r="C32" t="n">
-        <v>8.367855888830752</v>
+        <v>8.370895917941935</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1869,10 +1869,10 @@
         <v>872</v>
       </c>
       <c r="B33" t="n">
-        <v>16.61582568807339</v>
+        <v>16.61295871559633</v>
       </c>
       <c r="C33" t="n">
-        <v>8.367855888830752</v>
+        <v>8.370895917941935</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
